--- a/Excel/SoundTable.xlsx
+++ b/Excel/SoundTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MillenniumOfCultivation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94E5DBB-C5CE-44FF-8DCA-9E87C503C39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338DDB46-B295-4300-8BBD-3A23F782EF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8820" yWindow="1630" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="#SoundTable" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="29">
   <si>
     <t>FIELD</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,14 +106,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Resources/Sound/UI/Click.ogg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_UI_Click</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Background</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -123,6 +115,30 @@
   </si>
   <si>
     <t>UI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources/Sound/UI/00104.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_UI_Select</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_UI_Cancel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources/Sound/UI/00103.wav</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_UI_Confirm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources/Sound/UI/00106.wav</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -600,10 +616,10 @@
         <v>10000001</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>19</v>
@@ -618,13 +634,13 @@
         <v>10000002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" s="5"/>
     </row>
@@ -635,9 +651,15 @@
       <c r="B7" s="3">
         <v>10000003</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="5"/>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -647,9 +669,15 @@
       <c r="B8" s="3">
         <v>10000004</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
